--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.96243260905035</v>
+        <v>4.056395298970681</v>
       </c>
       <c r="D2" t="n">
-        <v>27.6922927943824</v>
+        <v>4.49999757908714</v>
       </c>
       <c r="E2" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F2" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.70623602141178</v>
+        <v>5.802263353479414</v>
       </c>
       <c r="D3" t="n">
-        <v>38.0184520329095</v>
+        <v>6.177998455347794</v>
       </c>
       <c r="E3" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F3" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.621017172042786</v>
+        <v>1.075915290456953</v>
       </c>
       <c r="D4" t="n">
-        <v>9.277107301012052</v>
+        <v>1.507529936414459</v>
       </c>
       <c r="E4" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F4" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.846217180943658</v>
+        <v>1.600010291903344</v>
       </c>
       <c r="D5" t="n">
-        <v>7.998141001022823</v>
+        <v>1.299697912666209</v>
       </c>
       <c r="E5" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F5" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.50764837075656</v>
+        <v>2.844992860247942</v>
       </c>
       <c r="D6" t="n">
-        <v>17.24027009241817</v>
+        <v>2.801543890017953</v>
       </c>
       <c r="E6" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F6" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.41692687038515</v>
+        <v>5.105250616437588</v>
       </c>
       <c r="D7" t="n">
-        <v>28.80792271639453</v>
+        <v>4.681287441414112</v>
       </c>
       <c r="E7" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F7" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.55809519790484</v>
+        <v>5.615690469659537</v>
       </c>
       <c r="D8" t="n">
-        <v>34.7922029814692</v>
+        <v>5.653732984488745</v>
       </c>
       <c r="E8" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F8" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.23249840704268</v>
+        <v>2.800280991144436</v>
       </c>
       <c r="D9" t="n">
-        <v>17.49554763443712</v>
+        <v>2.843026490596032</v>
       </c>
       <c r="E9" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F9" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.52019555583342</v>
+        <v>4.79703177782293</v>
       </c>
       <c r="D10" t="n">
-        <v>29.38920473601126</v>
+        <v>4.77574576960183</v>
       </c>
       <c r="E10" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F10" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.18420052716519</v>
+        <v>5.554932585664344</v>
       </c>
       <c r="D11" t="n">
-        <v>34.1055130723391</v>
+        <v>5.542145874255104</v>
       </c>
       <c r="E11" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F11" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.21665176965389</v>
+        <v>4.910205912568757</v>
       </c>
       <c r="D12" t="n">
-        <v>30.48718193213844</v>
+        <v>4.954167063972497</v>
       </c>
       <c r="E12" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F12" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.71153011856365</v>
+        <v>3.690623644266593</v>
       </c>
       <c r="D13" t="n">
-        <v>22.93461448239026</v>
+        <v>3.726874853388418</v>
       </c>
       <c r="E13" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F13" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>41.89351140349799</v>
+        <v>6.807695603068423</v>
       </c>
       <c r="D14" t="n">
-        <v>41.95529370573963</v>
+        <v>6.817735227182689</v>
       </c>
       <c r="E14" t="n">
-        <v>10.16675831446261</v>
+        <v>1.652098226100174</v>
       </c>
       <c r="F14" t="n">
-        <v>10.1761168274198</v>
+        <v>1.653618984455717</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
